--- a/Configs/GameConfig/Datas/expedition_reward_profile.xlsx
+++ b/Configs/GameConfig/Datas/expedition_reward_profile.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -73,6 +73,9 @@
     <t>weight</t>
   </si>
   <si>
+    <t>tier</t>
+  </si>
+  <si>
     <t>value</t>
   </si>
   <si>
@@ -85,7 +88,7 @@
     <t>##</t>
   </si>
   <si>
-    <t>配置1</t>
+    <t>奖励配置1</t>
   </si>
   <si>
     <t>early</t>
@@ -1304,31 +1307,31 @@
       <c r="D3" s="7"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3" s="11"/>
       <c r="L3" s="11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N3" s="11"/>
       <c r="O3" s="11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
@@ -1336,16 +1339,16 @@
     </row>
     <row r="4" s="2" customFormat="1" spans="1:19">
       <c r="A4" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" s="14"/>
       <c r="F4" s="14"/>
@@ -1365,7 +1368,7 @@
     </row>
     <row r="5" s="3" customFormat="1" spans="1:19">
       <c r="A5" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="16"/>
@@ -1388,7 +1391,7 @@
     </row>
     <row r="6" s="3" customFormat="1" spans="1:19">
       <c r="A6" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="16"/>
@@ -1411,7 +1414,7 @@
     </row>
     <row r="7" s="4" customFormat="1" ht="57" customHeight="1" spans="1:19">
       <c r="A7" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="19"/>
@@ -1434,55 +1437,55 @@
     </row>
     <row r="8" spans="1:19">
       <c r="B8" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G8" s="6">
         <v>10</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J8" s="6">
         <v>10</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M8" s="6">
         <v>10</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P8" s="6">
         <v>1</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S8" s="6">
         <v>10</v>
@@ -1490,34 +1493,34 @@
     </row>
     <row r="9" spans="1:19">
       <c r="F9" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G9" s="6">
         <v>25</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J9" s="6">
         <v>25</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M9" s="6">
         <v>25</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P9" s="6">
         <v>2</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S9" s="6">
         <v>10</v>
@@ -1525,34 +1528,34 @@
     </row>
     <row r="10" spans="1:19">
       <c r="F10" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G10" s="6">
         <v>50</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J10" s="6">
         <v>50</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M10" s="6">
         <v>50</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P10" s="6">
         <v>3</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S10" s="6">
         <v>10</v>
@@ -1560,25 +1563,25 @@
     </row>
     <row r="11" spans="1:19">
       <c r="F11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G11" s="6">
         <v>100</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J11" s="6">
         <v>100</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M11" s="6">
         <v>100</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P11" s="6">
         <v>4</v>
@@ -1586,25 +1589,25 @@
     </row>
     <row r="12" spans="1:19">
       <c r="F12" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G12" s="6">
         <v>200</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J12" s="6">
         <v>200</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M12" s="6">
         <v>200</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P12" s="6">
         <v>5</v>
@@ -1612,37 +1615,37 @@
     </row>
     <row r="13" spans="1:19">
       <c r="E13" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G13" s="6">
         <v>10</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J13" s="6">
         <v>10</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M13" s="6">
         <v>10</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P13" s="6">
         <v>1</v>
@@ -1650,25 +1653,25 @@
     </row>
     <row r="14" spans="1:19">
       <c r="F14" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G14" s="6">
         <v>25</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J14" s="6">
         <v>25</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M14" s="6">
         <v>25</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P14" s="6">
         <v>2</v>
@@ -1676,25 +1679,25 @@
     </row>
     <row r="15" spans="1:19">
       <c r="F15" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G15" s="6">
         <v>50</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J15" s="6">
         <v>50</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M15" s="6">
         <v>50</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P15" s="6">
         <v>3</v>
@@ -1702,25 +1705,25 @@
     </row>
     <row r="16" spans="1:19">
       <c r="F16" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G16" s="6">
         <v>100</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J16" s="6">
         <v>100</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M16" s="6">
         <v>100</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P16" s="6">
         <v>4</v>
@@ -1728,25 +1731,25 @@
     </row>
     <row r="17" spans="5:16">
       <c r="F17" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G17" s="6">
         <v>200</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J17" s="6">
         <v>200</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M17" s="6">
         <v>200</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P17" s="6">
         <v>5</v>
@@ -1754,37 +1757,37 @@
     </row>
     <row r="18" spans="5:16">
       <c r="E18" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G18" s="6">
         <v>10</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J18" s="6">
         <v>10</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M18" s="6">
         <v>10</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P18" s="6">
         <v>1</v>
@@ -1792,25 +1795,25 @@
     </row>
     <row r="19" spans="5:16">
       <c r="F19" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G19" s="6">
         <v>25</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J19" s="6">
         <v>25</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M19" s="6">
         <v>25</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P19" s="6">
         <v>2</v>
@@ -1818,25 +1821,25 @@
     </row>
     <row r="20" spans="5:16">
       <c r="F20" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G20" s="6">
         <v>50</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J20" s="6">
         <v>50</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M20" s="6">
         <v>50</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P20" s="6">
         <v>3</v>
@@ -1844,25 +1847,25 @@
     </row>
     <row r="21" spans="5:16">
       <c r="F21" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G21" s="6">
         <v>100</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J21" s="6">
         <v>100</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M21" s="6">
         <v>100</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P21" s="6">
         <v>4</v>
@@ -1870,25 +1873,25 @@
     </row>
     <row r="22" spans="5:16">
       <c r="F22" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G22" s="6">
         <v>200</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J22" s="6">
         <v>200</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M22" s="6">
         <v>200</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P22" s="6">
         <v>5</v>
